--- a/partner_results/uo/ClassMissingGermanDefinition_uo.xlsx
+++ b/partner_results/uo/ClassMissingGermanDefinition_uo.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>millimeter [uo]</t>
+          <t>kinematic viscosity [uo]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>measurement unit label</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"A length unit which is equal to one thousandth of a meter or 10^[-3] m." [NIST:NIST]</t>
+          <t>The ratio of the dynamic viscosity (μ) over the density of the fluid (ρ), which is noted as (length)^2/time. https://en.wikipedia.org/wiki/Viscosity#Kinematic_viscosity</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kinematic viscosity [uo]</t>
+          <t>millimeter [uo]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The ratio of the dynamic viscosity (μ) over the density of the fluid (ρ), which is noted as (length)^2/time. https://en.wikipedia.org/wiki/Viscosity#Kinematic_viscosity</t>
+          <t>"A length unit which is equal to one thousandth of a meter or 10^[-3] m." [NIST:NIST]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
